--- a/output/重要事項説明書_訪問介護_いいかいご.xlsx
+++ b/output/重要事項説明書_訪問介護_いいかいご.xlsx
@@ -77,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -100,10 +100,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -658,20 +654,20 @@
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t>事業所所在地</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>【要入力】</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>〒543-0023 大阪府大阪市天王寺区味原町13-18 オーセント味原302号室</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
@@ -680,16 +676,16 @@
 相談担当者名</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>TEL：【要入力】 FAX：【要入力】
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>TEL：06-4400-9333 FAX：06-4400-9332
 いいかいご事業部
 生田 友哉</t>
         </is>
       </c>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
@@ -2821,15 +2817,11 @@
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
-      <c r="A223" s="10" t="inlineStr">
-        <is>
-          <t>氏名 生田 友哉（連絡先：【要入力】）</t>
-        </is>
-      </c>
-      <c r="B223" s="11" t="n"/>
-      <c r="C223" s="11" t="n"/>
-      <c r="D223" s="11" t="n"/>
-      <c r="E223" s="11" t="n"/>
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>氏名 生田 友哉（連絡先：06-4400-9333）</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="45" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
@@ -2868,7 +2860,7 @@
         </is>
       </c>
     </row>
-    <row r="230" ht="60" customHeight="1">
+    <row r="230" ht="75" customHeight="1">
       <c r="A230" s="6" t="inlineStr">
         <is>
           <t>【事業者の窓口】
@@ -2878,15 +2870,15 @@
         </is>
       </c>
       <c r="B230" s="9" t="n"/>
-      <c r="C230" s="7" t="inlineStr">
-        <is>
-          <t>所在地　【要入力】
-電話番号・ﾌｧｯｸｽ番号　【要入力】
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>所在地　〒543-0023 大阪府大阪市天王寺区味原町13-18 オーセント味原302号室
+電話番号 06-4400-9333　ﾌｧｯｸｽ番号 06-4400-9332
 受付時間　午前9時～午後6時</t>
         </is>
       </c>
-      <c r="D230" s="8" t="n"/>
-      <c r="E230" s="8" t="n"/>
+      <c r="D230" s="4" t="n"/>
+      <c r="E230" s="4" t="n"/>
     </row>
     <row r="231" ht="60" customHeight="1">
       <c r="A231" s="6" t="inlineStr">
@@ -3501,96 +3493,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>法人名</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>株式会社AA → 株式会社dhpケアマネジメント（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>事業所名</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>ええかいご → いいかいご（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>管理者・サービス提供責任者等</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>抜屋 壮勇 → 生田 友哉（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>黄色セル</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>【要入力】：いいかいご／新法人の情報が手元にないため空欄。代表者氏名・本社所在地・法人設立年月日・事業所番号・事業所所在地・電話/FAX・苦情窓口所在地など</t>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>【要入力】：いいかいご／新法人の情報が手元にないため空欄。代表者氏名・本社所在地・法人設立年月日・指定事業所番号・署名欄の事業者所在地</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>コメント付きセル</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>旧事業所の内容をそのまま残した箇所（実施地域・損害賠償保険など）。要確認</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>説明年月日・利用者欄</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>新しく使えるよう空欄にしています</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>元の資料</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>重要事項説明書（訪問介護用）写真15ページ（重複1枚を除外）</t>
         </is>

--- a/output/重要事項説明書_訪問介護_いいかいご.xlsx
+++ b/output/重要事項説明書_訪問介護_いいかいご.xlsx
@@ -645,14 +645,14 @@
 事業所番号</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>大阪市指定【要入力】</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>大阪市指定２７７１７０２８２２</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>【要入力】：いいかいご／新法人の情報が手元にないため空欄。代表者氏名・本社所在地・法人設立年月日・指定事業所番号・署名欄の事業者所在地</t>
+          <t>【要入力】：いいかいご／新法人の情報が手元にないため空欄。代表者氏名・本社所在地・法人設立年月日・署名欄の事業者所在地</t>
         </is>
       </c>
     </row>

--- a/output/重要事項説明書_訪問介護_いいかいご.xlsx
+++ b/output/重要事項説明書_訪問介護_いいかいご.xlsx
@@ -191,11 +191,6 @@
     <author>Claude</author>
   </authors>
   <commentList>
-    <comment ref="B9" authorId="0" shapeId="0">
-      <text>
-        <t>法人変更のため要入力（旧：大石 佐智子）</t>
-      </text>
-    </comment>
     <comment ref="B19" authorId="0" shapeId="0">
       <text>
         <t>旧事業所の内容のまま。要確認</t>
@@ -567,14 +562,14 @@
           <t>代表者氏名</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>【要入力】</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>吉田 駿成</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -3074,13 +3069,13 @@
           <t>代表者名</t>
         </is>
       </c>
-      <c r="C250" s="7" t="inlineStr">
-        <is>
-          <t>【要入力】　　　　印</t>
-        </is>
-      </c>
-      <c r="D250" s="8" t="n"/>
-      <c r="E250" s="8" t="n"/>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>吉田 駿成　　　　印</t>
+        </is>
+      </c>
+      <c r="D250" s="4" t="n"/>
+      <c r="E250" s="4" t="n"/>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="6" t="inlineStr">
@@ -3548,7 +3543,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>【要入力】：いいかいご／新法人の情報が手元にないため空欄。代表者氏名・本社所在地・法人設立年月日・署名欄の事業者所在地</t>
+          <t>【要入力】：いいかいご／新法人の情報が手元にないため空欄。本社所在地・法人設立年月日・署名欄の事業者所在地</t>
         </is>
       </c>
     </row>

--- a/output/重要事項説明書_訪問介護_いいかいご.xlsx
+++ b/output/重要事項説明書_訪問介護_いいかいご.xlsx
@@ -41,7 +41,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -51,11 +51,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,18 +90,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -571,23 +559,23 @@
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t>本社所在地
 （連絡先及び電話番号等）</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>【要入力】
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>〒541-0058 大阪府大阪市中央区南久宝寺町四丁目5番17号 アップウェル船場 2F
 いいかいご
-TEL：【要入力】 FAX：【要入力】</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
+TEL：06-4400-9333 FAX：06-4400-9332</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -595,14 +583,14 @@
           <t>法人設立年月日</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>【要入力】</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>平成12年6月8日</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -843,8 +831,8 @@
           <t>職務内容</t>
         </is>
       </c>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
       <c r="E35" s="6" t="inlineStr">
         <is>
           <t>人員数</t>
@@ -962,14 +950,14 @@
           <t>サービス区分と種類</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n"/>
+      <c r="B43" s="7" t="n"/>
       <c r="C43" s="6" t="inlineStr">
         <is>
           <t>サービスの内容</t>
         </is>
       </c>
-      <c r="D43" s="9" t="n"/>
-      <c r="E43" s="9" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
     </row>
     <row r="44" ht="60" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
@@ -977,7 +965,7 @@
           <t>訪問介護計画の作成</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n"/>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="3" t="inlineStr">
         <is>
           <t>利用者に係る居宅介護支援事業者が作成した居宅サービス計画（ケアプラン）に基づき、利用者の意向や心身の状況等のアセスメントを行い、援助の目標に応じて具体的なサービス内容を定めた訪問介護計画を作成します。</t>
@@ -1289,7 +1277,7 @@
 通院等のための乗車又は降車の介助</t>
         </is>
       </c>
-      <c r="B60" s="9" t="n"/>
+      <c r="B60" s="7" t="n"/>
       <c r="C60" s="3" t="inlineStr">
         <is>
           <t>通院等に際して、訪問介護員等が運転する自動車への移動・移乗の介助を行います。（移送に係る運賃は別途必要になります。）</t>
@@ -1553,13 +1541,13 @@
           <t>20分以上45分未満（単位数179）</t>
         </is>
       </c>
-      <c r="C84" s="9" t="n"/>
+      <c r="C84" s="7" t="n"/>
       <c r="D84" s="6" t="inlineStr">
         <is>
           <t>45分以上（単位数220）</t>
         </is>
       </c>
-      <c r="E84" s="9" t="n"/>
+      <c r="E84" s="7" t="n"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
@@ -1704,7 +1692,7 @@
           <t>加算</t>
         </is>
       </c>
-      <c r="B94" s="9" t="n"/>
+      <c r="B94" s="7" t="n"/>
       <c r="C94" s="6" t="inlineStr">
         <is>
           <t>利用料</t>
@@ -1727,7 +1715,7 @@
           <t>特定事業所加算</t>
         </is>
       </c>
-      <c r="B95" s="9" t="n"/>
+      <c r="B95" s="7" t="n"/>
       <c r="C95" s="3" t="inlineStr">
         <is>
           <t>（Ⅰ）所定単位数の20/100
@@ -1754,7 +1742,7 @@
           <t>緊急時訪問介護加算</t>
         </is>
       </c>
-      <c r="B96" s="9" t="n"/>
+      <c r="B96" s="7" t="n"/>
       <c r="C96" s="3" t="inlineStr">
         <is>
           <t>1,112円</t>
@@ -1777,7 +1765,7 @@
           <t>初回加算</t>
         </is>
       </c>
-      <c r="B97" s="9" t="n"/>
+      <c r="B97" s="7" t="n"/>
       <c r="C97" s="3" t="inlineStr">
         <is>
           <t>2,224円</t>
@@ -1800,7 +1788,7 @@
           <t>中山間地域等における小規模事業所加算</t>
         </is>
       </c>
-      <c r="B98" s="9" t="n"/>
+      <c r="B98" s="7" t="n"/>
       <c r="C98" s="3" t="inlineStr">
         <is>
           <t>所定単位数の10/100</t>
@@ -1823,7 +1811,7 @@
           <t>中山間地域等に居住する者へのサービス提供加算</t>
         </is>
       </c>
-      <c r="B99" s="9" t="n"/>
+      <c r="B99" s="7" t="n"/>
       <c r="C99" s="3" t="inlineStr">
         <is>
           <t>所定単位数の5/100</t>
@@ -1847,7 +1835,7 @@
 生活機能向上連携加算(Ⅱ)</t>
         </is>
       </c>
-      <c r="B100" s="9" t="n"/>
+      <c r="B100" s="7" t="n"/>
       <c r="C100" s="3" t="inlineStr">
         <is>
           <t>(Ⅰ)1,112円
@@ -1873,7 +1861,7 @@
 訪問介護認知症専門ケア加算（Ⅱ）</t>
         </is>
       </c>
-      <c r="B101" s="9" t="n"/>
+      <c r="B101" s="7" t="n"/>
       <c r="C101" s="3" t="inlineStr">
         <is>
           <t>（Ⅰ）33円
@@ -1898,7 +1886,7 @@
           <t>口腔連携強化加算</t>
         </is>
       </c>
-      <c r="B102" s="9" t="n"/>
+      <c r="B102" s="7" t="n"/>
       <c r="C102" s="3" t="inlineStr">
         <is>
           <t>556円</t>
@@ -1922,7 +1910,7 @@
 （要介護度による区分なし）</t>
         </is>
       </c>
-      <c r="B103" s="9" t="n"/>
+      <c r="B103" s="7" t="n"/>
       <c r="C103" s="3" t="inlineStr">
         <is>
           <t>（Ⅰ）所定単位数の245/1000
@@ -2864,7 +2852,7 @@
 いいかいご事業部</t>
         </is>
       </c>
-      <c r="B230" s="9" t="n"/>
+      <c r="B230" s="7" t="n"/>
       <c r="C230" s="3" t="inlineStr">
         <is>
           <t>所在地　〒543-0023 大阪府大阪市天王寺区味原町13-18 オーセント味原302号室
@@ -2883,7 +2871,7 @@
 介護保険課</t>
         </is>
       </c>
-      <c r="B231" s="9" t="n"/>
+      <c r="B231" s="7" t="n"/>
       <c r="C231" s="3" t="inlineStr">
         <is>
           <t>所在地 大阪市中央区船場中央3-7-331
@@ -2904,7 +2892,7 @@
 （指定・指導グループ）</t>
         </is>
       </c>
-      <c r="B232" s="9" t="n"/>
+      <c r="B232" s="7" t="n"/>
       <c r="C232" s="3" t="inlineStr">
         <is>
           <t>大阪市中央区船場中央３丁目１番7-331
@@ -2922,7 +2910,7 @@
 大阪府国民健康保険団体連合会</t>
         </is>
       </c>
-      <c r="B233" s="9" t="n"/>
+      <c r="B233" s="7" t="n"/>
       <c r="C233" s="3" t="inlineStr">
         <is>
           <t>所在地 大阪市中央区常盤町1-3-8
@@ -3020,7 +3008,7 @@
       <c r="D246" s="4" t="n"/>
       <c r="E246" s="4" t="n"/>
     </row>
-    <row r="248" ht="18" customHeight="1">
+    <row r="248" ht="30" customHeight="1">
       <c r="A248" s="6" t="inlineStr">
         <is>
           <t>事業者</t>
@@ -3031,13 +3019,13 @@
           <t>所在地</t>
         </is>
       </c>
-      <c r="C248" s="7" t="inlineStr">
-        <is>
-          <t>【要入力】</t>
-        </is>
-      </c>
-      <c r="D248" s="8" t="n"/>
-      <c r="E248" s="8" t="n"/>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>〒541-0058 大阪府大阪市中央区南久宝寺町四丁目5番17号 アップウェル船場 2F</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="n"/>
+      <c r="E248" s="4" t="n"/>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="6" t="inlineStr">
@@ -3488,96 +3476,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>法人名</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>株式会社AA → 株式会社dhpケアマネジメント（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>事業所名</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>ええかいご → いいかいご（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>管理者・サービス提供責任者等</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>抜屋 壮勇 → 生田 友哉（ご指示どおり）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>黄色セル</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>【要入力】：いいかいご／新法人の情報が手元にないため空欄。本社所在地・法人設立年月日・署名欄の事業者所在地</t>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>要入力</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>なし（すべて入力済み）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>コメント付きセル</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>旧事業所の内容をそのまま残した箇所（実施地域・損害賠償保険など）。要確認</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>説明年月日・利用者欄</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>新しく使えるよう空欄にしています</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>元の資料</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>重要事項説明書（訪問介護用）写真15ページ（重複1枚を除外）</t>
         </is>

--- a/output/重要事項説明書_訪問介護_いいかいご.xlsx
+++ b/output/重要事項説明書_訪問介護_いいかいご.xlsx
@@ -179,11 +179,6 @@
     <author>Claude</author>
   </authors>
   <commentList>
-    <comment ref="B19" authorId="0" shapeId="0">
-      <text>
-        <t>旧事業所の内容のまま。要確認</t>
-      </text>
-    </comment>
     <comment ref="B22" authorId="0" shapeId="0">
       <text>
         <t>原本の「指定本文介護」は「指定訪問介護」の誤字と思われます（原本のまま）</t>
@@ -679,7 +674,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>大阪市西淀川区、大阪市淀川区、東淀川区</t>
+          <t>大阪市西淀川区、大阪市淀川区、東淀川区、天王寺区、中央区、北区</t>
         </is>
       </c>
       <c r="C19" s="4" t="n"/>
@@ -3543,7 +3538,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>旧事業所の内容をそのまま残した箇所（実施地域・損害賠償保険など）。要確認</t>
+          <t>旧事業所の内容をそのまま残した箇所（損害賠償保険など）。要確認</t>
         </is>
       </c>
     </row>

--- a/output/重要事項説明書_訪問介護_いいかいご.xlsx
+++ b/output/重要事項説明書_訪問介護_いいかいご.xlsx
@@ -1898,7 +1898,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="750" customHeight="1">
+    <row r="103" ht="120" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
           <t>介護職員等処遇改善加算
@@ -1911,21 +1911,7 @@
           <t>（Ⅰ）所定単位数の245/1000
 （Ⅱ）所定単位数の224/1000
 （Ⅲ）所定単位数の182/1000
-（Ⅳ）所定単位数の145/1000
-（Ⅴ1）所定単位数の221/1000
-（Ⅴ2）所定単位数の208/1000
-（Ⅴ3）所定単位数の200/1000
-（Ⅴ4）所定単位数の187/1000
-（Ⅴ5）所定単位数の184/1000
-（Ⅴ6）所定単位数の163/1000
-（Ⅴ7）所定単位数の163/1000
-（Ⅴ8）所定単位数の158/1000
-（Ⅴ9）所定単位数の142/1000
-（Ⅴ10）所定単位数の139/1000
-（Ⅴ11）所定単位数の121/1000
-（Ⅴ12）所定単位数の118/1000
-（Ⅴ13）所定単位数の100/1000
-（Ⅴ14）所定単位数の76/1000</t>
+（Ⅳ）所定単位数の145/1000</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -1935,8 +1921,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>基本サービス費に各種加算減算を加えた総単位数（所定単位数）
-※（Ⅴ）は令和7年3月31日まで算定可</t>
+          <t>基本サービス費に各種加算減算を加えた総単位数（所定単位数）</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2190,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>１提供当たりの料金の100%を請求いたします。</t>
+          <t>１提供当たりの利用者負担額の50%を請求いたします。</t>
         </is>
       </c>
       <c r="D141" s="4" t="n"/>
@@ -2224,7 +2209,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>１提供当たりの料金の50%を請求いたします。</t>
+          <t>１提供当たりの利用者負担額の100%を請求いたします。</t>
         </is>
       </c>
       <c r="D142" s="4" t="n"/>

--- a/output/重要事項説明書_訪問介護_いいかいご.xlsx
+++ b/output/重要事項説明書_訪問介護_いいかいご.xlsx
@@ -179,11 +179,6 @@
     <author>Claude</author>
   </authors>
   <commentList>
-    <comment ref="B22" authorId="0" shapeId="0">
-      <text>
-        <t>原本の「指定本文介護」は「指定訪問介護」の誤字と思われます（原本のまま）</t>
-      </text>
-    </comment>
     <comment ref="B188" authorId="0" shapeId="0">
       <text>
         <t>旧法人の加入内容のまま。要確認</t>
@@ -688,7 +683,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="75" customHeight="1">
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t>事業の目的</t>
@@ -696,7 +691,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>適正な運営を確保するために必要な人員及び運営管理に関する事項を定め、要介護状態（介護予防にあっては要支援状態）にある利用者に対し、指定訪問介護［指定介護予防介護訪問介護］の円滑な運営管理を図るとともに、利用者の意思及び人格を尊重し、利用者の立場にたった適切な指定本文介護［指定介護予防介護訪問介護］の提供を確保することを目的とする。</t>
+          <t>適正な運営を確保するために必要な人員及び運営管理に関する事項を定め、要介護状態にある利用者に対し、指定訪問介護の円滑な運営管理を図るとともに、利用者の意思及び人格を尊重し、利用者の立場にたった適切な指定訪問介護の提供を確保することを目的とする。</t>
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
